--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -548,7 +548,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>26710.1</v>
+        <v>27021.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>41.36</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>645.7954545454545</v>
+        <v>645.8209847036329</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>-0.06310475666570081</v>
+        <v>-0.06314879238861004</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02417794970986461</v>
+        <v>0.02390057361376673</v>
       </c>
     </row>
     <row r="8">
@@ -720,10 +720,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19781.63733766234</v>
+        <v>19782.41936287899</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.2593948604586902</v>
+        <v>-0.267891286533734</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21773.45503246753</v>
+        <v>21774.31579998634</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.1848231555678365</v>
+        <v>-0.1941750887735592</v>
       </c>
     </row>
     <row r="15"/>
@@ -4207,7 +4207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4298,6 +4298,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>27021.15</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>-0.06314879238859999</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -548,7 +548,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>27021.15</v>
+        <v>26909.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>41.84</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>645.8209847036329</v>
+        <v>645.9337493999041</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>-0.06314879238861004</v>
+        <v>-0.06282820079689311</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02390057361376673</v>
+        <v>0.02400384061449832</v>
       </c>
     </row>
     <row r="8">
@@ -720,10 +720,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19782.41936287899</v>
+        <v>19785.87350661821</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.267891286533734</v>
+        <v>-0.2647280707770384</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21774.31579998634</v>
+        <v>21778.11774226734</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.1941750887735592</v>
+        <v>-0.1906933680817501</v>
       </c>
     </row>
     <row r="15"/>
@@ -4207,7 +4207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4331,6 +4331,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>26909.6</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>-0.06282820079690001</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>26909.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>41.66</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.9621212121212122</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>645.9337493999041</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>-0.06282820079689311</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>3.787878787878785</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>20</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>8.651515151515149</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>19785.87350661821</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.2647280707770384</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>21778.11774226734</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>-0.1906933680817501</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.4964902325119865</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.187485712435659</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.2397444533599041</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.07932919915662173</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.05358245673183548</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.067356574714033</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -842,19 +857,19 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>-0.08343851123664425</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1194689782814169</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.08364948928813487</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.07300545928318969</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -867,19 +882,19 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.1020634367593765</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1081221877623236</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.0717715568996562</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="30" t="n">
         <v>0.08557799326179127</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="30" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -892,23 +907,22 @@
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.09342406440628293</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1462377435415317</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.09111867819044783</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="30" t="n">
         <v>0.06625721707288168</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="30" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1044,16 +1058,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>13469.25</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>35.5</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1063,16 +1077,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>14051.75</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>35.92</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1082,16 +1096,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>14308.9</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>36.44</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1101,16 +1115,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>14425.3</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>37.4</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1120,16 +1134,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>14344.75</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>30.54</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1139,16 +1153,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>14466.5</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>31.04</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1158,16 +1172,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>13879.35</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>29.73</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1177,16 +1191,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>13662.8</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>31.97</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1196,16 +1210,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>14223</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>33.31</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1215,16 +1229,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>13179.9</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1234,16 +1248,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>12927.6</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>31.41</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1253,16 +1267,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>13584.1</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1272,16 +1286,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>13462.85</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>32.7</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1291,16 +1305,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>12604.45</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>33.41</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1310,16 +1324,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>12159.35</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>36.76</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1329,16 +1343,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>12776.55</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>38.66</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1348,16 +1362,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>12699.4</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>37.44</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1367,16 +1381,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>12971.9</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>36.55</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1386,16 +1400,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>13212.25</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>37.11</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1405,16 +1419,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>13144.2</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>34.21</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1424,16 +1438,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>12597.6</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>32.74</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1443,16 +1457,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>12360.25</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1462,16 +1476,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>11747.1</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>30.86</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1481,16 +1495,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>12017.05</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>31.55</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1500,16 +1514,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>12613.95</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>33.09</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1519,16 +1533,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>12678.4</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>27.89</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1538,16 +1552,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>13767.5</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>30.06</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1557,16 +1571,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>14992.15</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>32.34</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1576,16 +1590,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>15095.9</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>31.85</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1595,16 +1609,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>15422.75</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>32.55</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1614,16 +1628,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>14683.65</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>30.37</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1633,16 +1647,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>16238.9</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>32.71</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1652,16 +1666,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>16831.8</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>33.91</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1671,16 +1685,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>17938.65</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>36.05</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1690,16 +1704,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>19003.15</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>36.28</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1709,16 +1723,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>18996.15</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>36.57</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1728,16 +1742,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>18970.6</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>36.57</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1747,16 +1761,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>18796.3</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>34.15</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1766,16 +1780,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>19731.55</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>35.76</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1785,16 +1799,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>21777.15</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>39.27</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1804,16 +1818,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>23217.6</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>38.77</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1823,16 +1837,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>23281.2</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>38.79</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1842,16 +1856,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>22735.55</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>37.34</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1861,16 +1875,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>22240.2</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>35.12</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1880,16 +1894,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>23412.25</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>37.04</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1899,16 +1913,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>21438.6</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>33.31</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1918,16 +1932,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>19813.5</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>29.95</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1937,16 +1951,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>21137.45</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>32.02</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1956,16 +1970,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>21772.45</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>32.82</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1975,16 +1989,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>21442.05</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>30.7</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1994,16 +2008,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>22038.7</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>31.61</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2013,16 +2027,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>22771.05</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>32.34</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2032,16 +2046,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>21804.05</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>31.63</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2051,16 +2065,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>21454.25</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>33.07</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2070,16 +2084,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>22175.4</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>33.94</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2089,16 +2103,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>22998.3</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>34.01</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2108,16 +2122,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>22723.65</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>33.57</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2127,16 +2141,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>21715.1</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>33.1</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2146,16 +2160,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>22952.35</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>34.35</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2165,16 +2179,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>22232.25</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>33.28</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2184,16 +2198,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>23267.7</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>34.83</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2203,16 +2217,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>24345.8</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>37.61</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2222,16 +2236,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>25326.4</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>38.69</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2241,16 +2255,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>26534.8</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>42.93</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2260,16 +2274,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>27186.45</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>42.09</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2371,13 +2385,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>11963.5</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>60.61</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2385,12 +2399,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2398,31 +2412,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>10989.15</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>41.53</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2430,12 +2444,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2443,31 +2457,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>11142</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>43.05</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2475,12 +2489,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2488,31 +2502,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>11461</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>42.96</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2520,12 +2534,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2533,28 +2547,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>10267</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>38.14</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2562,15 +2576,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2578,28 +2592,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>10411.15</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>37.42</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2607,15 +2621,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2623,28 +2637,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>9606.4</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>35.45</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2652,15 +2666,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2668,28 +2682,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>9172.6</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>45.1</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2697,15 +2711,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2713,28 +2727,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>9620.1</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>47.19</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2742,15 +2756,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2758,28 +2772,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>8358.049999999999</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>45.43</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2787,15 +2801,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2803,28 +2817,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>9173.15</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>52.24</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2832,15 +2846,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2848,28 +2862,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>9972.450000000001</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>49.35</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2877,15 +2891,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2893,28 +2907,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>8868.700000000001</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>48.81</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2922,15 +2936,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2938,28 +2952,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>9346.549999999999</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>52.73</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2967,15 +2981,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2983,28 +2997,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>8065.15</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>38.4</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3012,15 +3026,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3028,28 +3042,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>7547.75</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>29.51</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3057,15 +3071,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3073,28 +3087,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>8040.15</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>25.8</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3102,15 +3116,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3118,28 +3132,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>7176.5</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>22.16</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3147,15 +3161,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3163,28 +3177,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>9985.15</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>30.49</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3192,15 +3206,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3208,28 +3222,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>11772.85</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>33.72</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3237,15 +3251,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3253,28 +3267,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>12915.9</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>38.43</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3282,15 +3296,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3298,28 +3312,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>12272.6</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>32.34</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3327,15 +3341,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3343,28 +3357,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>14308.9</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>36.44</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3372,15 +3386,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3388,28 +3402,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>14466.5</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>31.04</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3417,15 +3431,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3433,25 +3447,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>14223</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>33.31</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3459,15 +3473,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3475,25 +3489,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>13584.1</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>33</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3501,15 +3515,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3517,25 +3531,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>12159.35</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>36.76</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3543,15 +3557,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3559,25 +3573,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>12971.9</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>36.55</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3585,15 +3599,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3601,25 +3615,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>12597.6</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>32.74</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3627,15 +3641,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3643,25 +3657,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>12017.05</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>31.55</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3669,15 +3683,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3685,25 +3699,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>13767.5</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>30.06</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3711,15 +3725,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3727,25 +3741,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>15422.75</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>32.55</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3753,15 +3767,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3769,22 +3783,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>16831.8</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>33.91</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3792,15 +3806,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3808,22 +3822,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>18996.15</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>36.57</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3831,15 +3845,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3847,22 +3861,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>19731.55</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>35.76</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3870,15 +3884,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3886,22 +3900,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>23281.2</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>38.79</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3909,15 +3923,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3925,22 +3939,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>23412.25</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>37.04</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3948,15 +3962,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3964,22 +3978,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>21137.45</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>32.02</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3987,15 +4001,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4003,22 +4017,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>22038.7</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>31.61</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4026,15 +4040,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4042,22 +4056,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>21454.25</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>33.07</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4065,15 +4079,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4081,19 +4095,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>22723.65</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>33.57</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4101,15 +4115,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4117,19 +4131,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>22232.25</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>33.28</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4137,15 +4151,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4153,19 +4167,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>25326.4</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>38.69</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4173,15 +4187,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4189,10 +4203,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4269,30 +4283,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>26710.1</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>41.36</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.962121212121</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>-0.06310475666569999</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4302,30 +4316,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>27021.15</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>41.84</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.962121212121</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>-0.06314879238859999</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4335,30 +4349,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>26909.6</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>41.66</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.962121212121</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>-0.06282820079690001</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4478,4 +4492,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Pharma Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4391,6 +4394,512 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Pharma Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Abbott India Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ajanta Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Biocon Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cipla Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gland Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Laurus Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mankind Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Piramal Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sai Life Sciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Wockhardt Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4492,43 +5001,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Pharma Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26909.6</v>
+        <v>27152.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.66</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>645.9337493999041</v>
+        <v>645.8634633682207</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06282820079689311</v>
+        <v>-0.06302572570364084</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02400384061449832</v>
+        <v>0.02378686964795433</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19785.87350661821</v>
+        <v>19783.72054505912</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2647280707770384</v>
+        <v>-0.2713742014408047</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21778.11774226734</v>
+        <v>21775.74799850482</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1906933680817501</v>
+        <v>-0.1980086991980428</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4381,6 +4381,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>27152.1</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.0630257257036</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27152.1</v>
+        <v>27028.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>42.04</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>645.8634633682207</v>
+        <v>645.847072879331</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06302572570364084</v>
+        <v>-0.06299806564910615</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02378686964795433</v>
+        <v>0.02389486260454002</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19783.72054505912</v>
+        <v>19783.21848096945</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2713742014408047</v>
+        <v>-0.2680662229049325</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21775.74799850482</v>
+        <v>21775.19538146441</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1980086991980428</v>
+        <v>-0.1943676395289299</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4414,6 +4414,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>27028.7</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.0629980656491</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4454,7 +4487,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27028.7</v>
+        <v>27003</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.85</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>645.847072879331</v>
+        <v>645.8502750538148</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06299806564910615</v>
+        <v>-0.06286075105829292</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02389486260454002</v>
+        <v>0.02391772303276728</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19783.21848096945</v>
+        <v>19783.31656814842</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2680662229049325</v>
+        <v>-0.2673659753305772</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21775.19538146441</v>
+        <v>21775.3033450644</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1943676395289299</v>
+        <v>-0.1935968838623707</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4447,6 +4447,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>27003</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.0628607510583</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4487,7 +4520,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27003</v>
+        <v>26761.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.81</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>645.8502750538148</v>
+        <v>645.7927123552124</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06286075105829292</v>
+        <v>-0.06316337666071703</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02391772303276728</v>
+        <v>0.02413127413127413</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19783.31656814842</v>
+        <v>19781.55334045781</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2673659753305772</v>
+        <v>-0.2608246001103144</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21775.3033450644</v>
+        <v>21773.36257756481</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1935968838623707</v>
+        <v>-0.1863968560397132</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4480,6 +4480,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>26761.65</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.0631633766607</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4520,7 +4553,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26761.65</v>
+        <v>26933.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.44</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>645.7927123552124</v>
+        <v>645.8908872901678</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06316337666071703</v>
+        <v>-0.06283218171752525</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02413127413127413</v>
+        <v>0.02398081534772182</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.63142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19781.55334045781</v>
+        <v>19784.5605789654</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2608246001103144</v>
+        <v>-0.2654333675916412</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.71571428571428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21773.36257756481</v>
+        <v>21776.67261562178</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1863968560397132</v>
+        <v>-0.1914696813977391</v>
       </c>
     </row>
     <row r="16">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4513,6 +4513,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>26933.65</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.962121212121</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>-0.0628321817175</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4553,7 +4586,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26933.65</v>
+        <v>26438</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.7</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9621212121212122</v>
+        <v>0.9552238805970149</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>645.8908872901678</v>
+        <v>646.4058679706602</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.06283218171752525</v>
+        <v>-0.003617369342217347</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02398081534772182</v>
+        <v>0.02444987775061125</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>3.787878787878785</v>
+        <v>4.477611940298509</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>8.651515151515149</v>
+        <v>9.134328358208956</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>30.63142857142857</v>
+        <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19784.5605789654</v>
+        <v>19809.20016765631</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2654333675916412</v>
+        <v>-0.2507300034928395</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>33.71571428571428</v>
+        <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21776.67261562178</v>
+        <v>21907.06424030737</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1914696813977391</v>
+        <v>-0.1713796716730703</v>
       </c>
     </row>
     <row r="16">
@@ -821,7 +821,7 @@
         <v>0.187485712435659</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.2397444533599041</v>
+        <v>0.2383283063083881</v>
       </c>
       <c r="F18" s="30" t="n"/>
       <c r="G18" s="30" t="n">
@@ -835,20 +835,20 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.07932919915662173</v>
+        <v>0.05179432713028298</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.05358245673183548</v>
+        <v>0.1254754881957747</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.067356574714033</v>
       </c>
       <c r="F19" s="30" t="n"/>
       <c r="G19" s="30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -858,22 +858,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>-0.08343851123664425</v>
+        <v>0.02430175541291046</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1194689782814169</v>
+        <v>0.09228330585944167</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.08364948928813487</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>0.07300545928318969</v>
+        <v>0.08009167092390945</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.1020634367593765</v>
+        <v>0.1127228412072971</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.1081221877623236</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>-0.09342406440628293</v>
+        <v>-0.1071056810587691</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>0.1462377435415317</v>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -973,7 +973,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2292,6 +2292,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>26438</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2408,7 +2427,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2453,7 +2472,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2498,7 +2517,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2543,7 +2562,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2562,7 +2581,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2588,7 +2610,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2633,7 +2655,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2678,7 +2700,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2723,7 +2745,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2768,7 +2790,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2813,7 +2835,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2858,7 +2880,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2903,7 +2925,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2948,7 +2970,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2993,7 +3015,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3038,7 +3060,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3083,7 +3105,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3128,7 +3150,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3173,7 +3195,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3218,7 +3240,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3263,7 +3285,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3308,7 +3330,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3353,7 +3375,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3398,7 +3420,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3443,7 +3465,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3458,7 +3480,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3485,7 +3510,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3527,7 +3552,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3569,7 +3594,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3611,7 +3636,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3653,7 +3678,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3695,7 +3720,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3737,7 +3762,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3779,7 +3804,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3790,7 +3815,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3818,7 +3846,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3857,7 +3885,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3896,7 +3924,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3935,7 +3963,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3974,7 +4002,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4013,7 +4041,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4052,7 +4080,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4091,14 +4119,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4127,7 +4158,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4163,7 +4194,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4199,7 +4230,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4210,6 +4241,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>26438</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4224,15 +4291,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4546,6 +4613,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>26438</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.955223880597</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.00361736934222</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4586,7 +4686,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26438</v>
+        <v>26311.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9552238805970149</v>
+        <v>0.9477611940298507</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4058679706602</v>
+        <v>646.47542997543</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003617369342217347</v>
+        <v>-0.003523274936070964</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02444987775061125</v>
+        <v>0.02457002457002457</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>4.477611940298509</v>
+        <v>5.223880597014929</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.134328358208956</v>
+        <v>9.656716417910451</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19809.20016765631</v>
+        <v>19811.3319052299</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2507300034928395</v>
+        <v>-0.247048087048087</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21907.06424030737</v>
+        <v>21909.42173639873</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1713796716730703</v>
+        <v>-0.1673078273078276</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4646,6 +4646,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>26311.55</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>-0.00352327493607</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4686,7 +4719,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26311.55</v>
+        <v>26117.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.47542997543</v>
+        <v>646.4628712871287</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003523274936070964</v>
+        <v>-0.003697767582456213</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02457002457002457</v>
+        <v>0.02475247524752475</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19811.3319052299</v>
+        <v>19810.94704243281</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.247048087048087</v>
+        <v>-0.2414568599717114</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21909.42173639873</v>
+        <v>21908.99611527581</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1673078273078276</v>
+        <v>-0.1611244695898163</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4679,6 +4679,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>26117.1</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>-0.00369776758246</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4719,7 +4752,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26117.1</v>
+        <v>26549.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>40.4</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9477611940298507</v>
+        <v>0.9626865671641791</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4628712871287</v>
+        <v>646.4475286096907</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003697767582456213</v>
+        <v>-0.003609137095649362</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02475247524752475</v>
+        <v>0.02434867299732165</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>5.223880597014929</v>
+        <v>3.731343283582089</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.656716417910451</v>
+        <v>8.611940298507463</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19810.94704243281</v>
+        <v>19810.47686389092</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2414568599717114</v>
+        <v>-0.2538314376152214</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21908.99611527581</v>
+        <v>21908.47614317019</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1611244695898163</v>
+        <v>-0.1748095585933427</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4712,6 +4712,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>26549.6</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.962686567164</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>-0.00360913709565</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4752,7 +4785,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26549.6</v>
+        <v>26436.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.07</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9626865671641791</v>
+        <v>0.9552238805970149</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4475286096907</v>
+        <v>646.3704156479217</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003609137095649362</v>
+        <v>-0.00393838203400898</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02434867299732165</v>
+        <v>0.02444987775061125</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>3.731343283582089</v>
+        <v>4.477611940298509</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>8.611940298507463</v>
+        <v>9.134328358208956</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19810.47686389092</v>
+        <v>19808.11372616137</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2538314376152214</v>
+        <v>-0.2507300034928397</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21908.47614317019</v>
+        <v>21905.86274083129</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1748095585933427</v>
+        <v>-0.1713796716730704</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4745,6 +4745,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>26436.55</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.955223880597</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.00393838203401</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4785,7 +4818,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26436.55</v>
+        <v>25823.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>40.9</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9552238805970149</v>
+        <v>0.9477611940298507</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.3704156479217</v>
+        <v>646.389236545682</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.00393838203400898</v>
+        <v>-0.003646974189916219</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02444987775061125</v>
+        <v>0.02503128911138924</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>4.477611940298509</v>
+        <v>5.223880597014929</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.134328358208956</v>
+        <v>9.656716417910451</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19808.11372616137</v>
+        <v>19808.69049526193</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2507300034928397</v>
+        <v>-0.2329125692830324</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21905.86274083129</v>
+        <v>21906.50059181119</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1713796716730704</v>
+        <v>-0.1516753084212411</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4778,6 +4778,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>25823.25</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.00364697418992</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4818,7 +4851,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25823.25</v>
+        <v>25962.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.95</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.389236545682</v>
+        <v>646.4653884462152</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003646974189916219</v>
+        <v>-0.003610708173405697</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02503128911138924</v>
+        <v>0.0249003984063745</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19808.69049526193</v>
+        <v>19811.02418113262</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2329125692830324</v>
+        <v>-0.2369237336368809</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21906.50059181119</v>
+        <v>21909.08142323563</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1516753084212411</v>
+        <v>-0.1561112692088787</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4811,6 +4811,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>25962.05</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.00361070817341</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4851,7 +4884,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25962.05</v>
+        <v>26078.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>40.16</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4653884462152</v>
+        <v>646.4762022806146</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003610708173405697</v>
+        <v>-0.003731384511010183</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0249003984063745</v>
+        <v>0.02478929102627665</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19811.02418113262</v>
+        <v>19811.35557263262</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2369237336368809</v>
+        <v>-0.2403286351724627</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21909.08142323563</v>
+        <v>21909.44791026276</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1561112692088787</v>
+        <v>-0.1598767618103268</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4844,6 +4844,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>26078.85</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.00373138451101</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4884,7 +4917,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26078.85</v>
+        <v>26075</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4762022806146</v>
+        <v>646.3807635101635</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003731384511010183</v>
+        <v>-0.00387074467947468</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19811.35557263262</v>
+        <v>19808.43083787804</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2403286351724627</v>
+        <v>-0.2403286351724626</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21909.44791026276</v>
+        <v>21906.21343579573</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1598767618103268</v>
+        <v>-0.1598767618103267</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4877,6 +4877,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>26075</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.00387074467947</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4917,7 +4950,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26075</v>
+        <v>25736.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>40.34</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.3807635101635</v>
+        <v>646.4945993468978</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.00387074467947468</v>
+        <v>-0.003531357019221804</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02478929102627665</v>
+        <v>0.02511931675458427</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19808.43083787804</v>
+        <v>19811.91935335702</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2403286351724626</v>
+        <v>-0.2302149495819428</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21906.21343579573</v>
+        <v>21910.0713973517</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1598767618103267</v>
+        <v>-0.1486920012918508</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4910,6 +4910,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>25736.95</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.00353135701922</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4950,7 +4983,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25736.95</v>
+        <v>25817.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.81</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4945993468978</v>
+        <v>646.4146219328994</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003531357019221804</v>
+        <v>-0.003590777397116551</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02511931675458427</v>
+        <v>0.02503755633450176</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19811.91935335702</v>
+        <v>19809.46843407969</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2302149495819428</v>
+        <v>-0.2327205093354316</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21910.0713973517</v>
+        <v>21907.36091708992</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1486920012918508</v>
+        <v>-0.1514629086486874</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4943,6 +4943,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>25817.8</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>-0.00359077739712</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4983,7 +5016,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25817.8</v>
+        <v>25781.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.94</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4146219328994</v>
+        <v>646.4806920762287</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003590777397116551</v>
+        <v>-0.003510931492403335</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02503755633450176</v>
+        <v>0.02507522567703109</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19809.46843407969</v>
+        <v>19811.49316306061</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2327205093354316</v>
+        <v>-0.2315661269522854</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21907.36091708992</v>
+        <v>21909.60007200171</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1514629086486874</v>
+        <v>-0.1501862731050296</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4976,6 +4976,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>25781.65</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>-0.0035109314924</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5016,7 +5049,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25781.65</v>
+        <v>25615</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.88</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4806920762287</v>
+        <v>646.5169106511863</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003510931492403335</v>
+        <v>-0.00351491162902029</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02507522567703109</v>
+        <v>0.02523977788995457</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19811.49316306061</v>
+        <v>19812.60308646427</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2315661269522854</v>
+        <v>-0.2265234008797864</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21909.60007200171</v>
+        <v>21910.82754020336</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1501862731050296</v>
+        <v>-0.144609504579217</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5009,6 +5009,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>25615</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>-0.00351491162902</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5049,7 +5082,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25615</v>
+        <v>25565.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.62</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.5169106511863</v>
+        <v>646.4197218710494</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.00351491162902029</v>
+        <v>-0.003772285608467985</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02523977788995457</v>
+        <v>0.02528445006321113</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19812.60308646427</v>
+        <v>19809.62472241286</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2265234008797864</v>
+        <v>-0.2251544157486002</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21910.82754020336</v>
+        <v>21907.53375690807</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.144609504579217</v>
+        <v>-0.143095539100596</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5042,6 +5042,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>25565.9</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>-0.00377228560847</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5082,7 +5115,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25565.9</v>
+        <v>25596.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.55</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4197218710494</v>
+        <v>646.3800505050505</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003772285608467985</v>
+        <v>-0.003833425008982538</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02528445006321113</v>
+        <v>0.02525252525252525</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19809.62472241286</v>
+        <v>19808.40898773449</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2251544157486002</v>
+        <v>-0.2261327561327562</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21907.53375690807</v>
+        <v>21906.18927164501</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.143095539100596</v>
+        <v>-0.1441774891774895</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5075,6 +5075,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>25596.65</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>-0.00383342500898</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5115,7 +5148,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25596.65</v>
+        <v>25329.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.6</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9477611940298507</v>
+        <v>0.9328358208955224</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.3800505050505</v>
+        <v>646.489280245023</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003833425008982538</v>
+        <v>-0.003576155218680266</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02525252525252525</v>
+        <v>0.02552322613578356</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>5.223880597014929</v>
+        <v>6.716417910447758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.656716417910451</v>
+        <v>10.70149253731343</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19808.40898773449</v>
+        <v>19811.7563487202</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2261327561327562</v>
+        <v>-0.2178370888937504</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21906.18927164501</v>
+        <v>21909.89112994968</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1441774891774895</v>
+        <v>-0.1350032815576462</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5108,6 +5108,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>25329.45</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>-0.00357615521868</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5148,7 +5181,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25329.45</v>
+        <v>25774.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.18</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.9477611940298507</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.489280245023</v>
+        <v>646.4572360170555</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003576155218680266</v>
+        <v>-0.003597637772467022</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02552322613578356</v>
+        <v>0.02508151492350138</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>6.716417910447758</v>
+        <v>5.223880597014929</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>10.70149253731343</v>
+        <v>9.656716417910451</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19811.7563487202</v>
+        <v>19810.77434877638</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2178370888937504</v>
+        <v>-0.2313733920957396</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21909.89112994968</v>
+        <v>21908.80513275287</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1350032815576462</v>
+        <v>-0.1499731269482965</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5141,6 +5141,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>25774.25</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.94776119403</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>-0.00359763777247</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5181,7 +5214,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>25774.25</v>
+        <v>26267.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>39.87</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9477611940298507</v>
+        <v>0.9626865671641791</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>646.4572360170555</v>
+        <v>637.5546116504854</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003597637772467022</v>
+        <v>-0.01725190518053499</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02508151492350138</v>
+        <v>0.02427184466019417</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>5.223880597014929</v>
+        <v>3.731343283582089</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>9.656716417910451</v>
+        <v>8.611940298507463</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19810.77434877638</v>
+        <v>19537.95215325936</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2313733920957396</v>
+        <v>-0.2561858529819695</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21908.80513275287</v>
+        <v>21607.09010575589</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1499731269482965</v>
+        <v>-0.1774133148404996</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5174,6 +5174,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>26267.25</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.962686567164</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>-0.0172519051805</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5214,7 +5247,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26267.25</v>
+        <v>26541.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>41.2</v>
+        <v>42.15</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9626865671641791</v>
+        <v>0.9776119402985075</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>637.5546116504854</v>
+        <v>629.6880189798339</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.01725190518053499</v>
+        <v>-0.02932919338056883</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02427184466019417</v>
+        <v>0.02372479240806643</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>3.731343283582089</v>
+        <v>2.238805970149249</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>8.611940298507463</v>
+        <v>7.567164179104474</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19537.95215325936</v>
+        <v>19296.8792970683</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2561858529819695</v>
+        <v>-0.2729503473987459</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21607.09010575589</v>
+        <v>21340.4867849517</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1774133148404996</v>
+        <v>-0.1959532282663956</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5207,6 +5207,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>26541.35</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.977611940299</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>-0.0293291933806</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5247,7 +5280,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26541.35</v>
+        <v>26710.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>42.15</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>629.6880189798339</v>
+        <v>629.6746817538897</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.02932919338056883</v>
+        <v>-0.02927012999819434</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02372479240806643</v>
+        <v>0.02357378595002357</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19296.8792970683</v>
+        <v>19296.47057587391</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2729503473987459</v>
+        <v>-0.2775779618778204</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21340.4867849517</v>
+        <v>21340.03477874317</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1959532282663956</v>
+        <v>-0.2010709234188727</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5240,6 +5240,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>26710.8</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.977611940299</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>-0.0292701299982</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5280,7 +5313,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-pharma.xlsx
+++ b/docs/downloads/indices/nifty-pharma.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>26710.8</v>
+        <v>27124.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>42.42</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>629.6746817538897</v>
+        <v>635.5400656044985</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.02927012999819434</v>
+        <v>-0.02067625843473608</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02357378595002357</v>
+        <v>0.02343017806935333</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>30.64514285714286</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>19296.47057587391</v>
+        <v>19476.2161018878</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2775779618778204</v>
+        <v>-0.2819788458963718</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>33.89057142857142</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21340.03477874317</v>
+        <v>21538.81598908822</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.2010709234188727</v>
+        <v>-0.2059378765564335</v>
       </c>
     </row>
     <row r="16">
@@ -4291,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5273,6 +5273,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>27124.85</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.977611940299</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>-0.0206762584347</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5313,7 +5346,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
